--- a/tables/ae_per_anomaly_type_metrics.xlsx
+++ b/tables/ae_per_anomaly_type_metrics.xlsx
@@ -453,14 +453,14 @@
         <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="D2" t="n">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.510</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
         <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D3" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.682</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_anomaly_type_metrics.xlsx
+++ b/tables/ae_per_anomaly_type_metrics.xlsx
@@ -453,14 +453,14 @@
         <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="D2" t="n">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.510</t>
+          <t>0.491</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
         <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="D3" t="n">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>0.652</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_anomaly_type_metrics.xlsx
+++ b/tables/ae_per_anomaly_type_metrics.xlsx
@@ -453,14 +453,14 @@
         <v>627</v>
       </c>
       <c r="C2" t="n">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="D2" t="n">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.522</t>
         </is>
       </c>
     </row>
@@ -474,14 +474,14 @@
         <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>404</v>
+        <v>423</v>
       </c>
       <c r="D3" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.682</t>
         </is>
       </c>
     </row>

--- a/tables/ae_per_anomaly_type_metrics.xlsx
+++ b/tables/ae_per_anomaly_type_metrics.xlsx
@@ -419,12 +419,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Anomaly Type</t>
+          <t>Anomalietyp</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>Anzahl</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
